--- a/MES_servers_list.xlsx
+++ b/MES_servers_list.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -429,6 +429,8 @@
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,6 +474,16 @@
           <t>ShortName</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>WebAPI_URL</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>DAServer</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +521,16 @@
           <t>BCN - GBU - SAMPLE</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>http://es-bcn-s01.eua.companysite.com/ProcessData/AtProcessDataREST.dll</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ES-BCN-S01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -547,6 +569,16 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>NY - GBU - SAMPLE</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://us-nw-s03.nam.companysite.com/piwebapi</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PIDASERVER</t>
         </is>
       </c>
     </row>

--- a/MES_servers_list.xlsx
+++ b/MES_servers_list.xlsx
@@ -418,167 +418,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>zone</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>server</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>atelier</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DirectoryHost</t>
+          <t>WebAPI_URL</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ShortName</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>WebAPI_URL</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>DAServer</t>
+          <t>PI_AF_Server</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>Barcelona GBU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>ES-BCN-S01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GBU Bcn</t>
+          <t>IP21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ES-BCN-S01</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>eua.companysite.com</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>IP21</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>BCN - GBU - SAMPLE</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>http://es-bcn-s01.eua.companysite.com/ProcessData/AtProcessDataREST.dll</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ES-BCN-S01</t>
+          <t>es-bcn-s01.eua.companysite.com</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>New York GBU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New-york</t>
+          <t>PIDASERVER</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GBU NY</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>US-NW-S03</t>
+          <t>https://us-nw-s03.nam.companysite.com/piwebapi/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>nam.companysite.com</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>5450</v>
-      </c>
-      <c r="G3" t="inlineStr">
+          <t>NY-AF01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>US-TX-S02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>PI</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>NY - GBU - SAMPLE</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>https://us-nw-s03.nam.companysite.com/piwebapi</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>PIDASERVER</t>
         </is>
       </c>
     </row>

--- a/MES_servers_list.xlsx
+++ b/MES_servers_list.xlsx
@@ -515,6 +515,11 @@
           <t>PI</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>us-tx-s02.nam.companysite.com/piwebapi</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/MES_servers_list.xlsx
+++ b/MES_servers_list.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -454,6 +454,11 @@
           <t>PI_AF_Server</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>AF_Database</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
